--- a/xxxx/gui_competition_eval/code-for-student/output_quick/result.xlsx
+++ b/xxxx/gui_competition_eval/code-for-student/output_quick/result.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>14</v>
